--- a/InputData/bldgs/BPSfDSPC/BAU Perc Subsidy for Distributed Solar PV Capacity.xlsx
+++ b/InputData/bldgs/BPSfDSPC/BAU Perc Subsidy for Distributed Solar PV Capacity.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\bldgs\BPSfDSPC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kjh_local\NEXTgroup_local\2025_local\2. EPS\업데이트 파일\eps-southkorea-3.3.1_2025update_v4.0.3\InputData\bldgs\BPSfDSPC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B358AC65-4386-4D6B-A447-C59C227A0A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B028CEF2-967D-41C7-A55F-8A6892A82247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="7" r:id="rId1"/>
-    <sheet name="BPSfDSPV" sheetId="8" r:id="rId2"/>
+    <sheet name="BPSfDSPC" sheetId="8" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Sources:</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>None needed</t>
+  </si>
+  <si>
+    <t>BPSfDSPC BAU Percent Subsidy for Distributed Solar PV Capacity</t>
   </si>
   <si>
     <r>
@@ -59,26 +62,44 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">We include the 30% 25D credit included in the Inflation Reduction Act, which is phased out through 2035. </t>
     </r>
-  </si>
-  <si>
-    <t>BPSfDSPC BAU Percent Subsidy for Distributed Solar PV Capacity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>태양광 설치단가 출처</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>태양광 지원금 단가 출처</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.knrec.or.kr/biz/introduce/new_engy/intro_home.do?utm_source=chatgpt.com</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://blog.naver.com/solarconnect/223140144171</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>비율은 (보조금단가)/(설치단가) 로 산정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -86,8 +107,31 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -108,8 +152,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -118,14 +163,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -141,9 +187,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -181,9 +227,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -216,26 +262,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -268,26 +297,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -461,54 +473,81 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="61.5703125" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="61.625" customWidth="1"/>
+    <col min="5" max="5" width="9.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B8" r:id="rId1" xr:uid="{720CE5BB-68CA-47F5-B713-5AE12D412E26}"/>
+    <hyperlink ref="B7" r:id="rId2" xr:uid="{96D822C4-E724-4820-82B2-21629B893110}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet2">
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="25.875" customWidth="1"/>
+    <col min="2" max="2" width="18.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="B1">
@@ -602,302 +641,474 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
-        <v>0</v>
-      </c>
-      <c r="C2" s="6">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="E2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="G2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="H2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="I2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="J2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="K2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="L2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="M2" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="N2" s="6">
-        <v>0.26</v>
-      </c>
-      <c r="O2" s="6">
-        <v>0.22</v>
-      </c>
-      <c r="P2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="6">
-        <v>0</v>
-      </c>
-      <c r="R2" s="6">
-        <v>0</v>
-      </c>
-      <c r="S2" s="6">
-        <v>0</v>
-      </c>
-      <c r="T2" s="6">
-        <v>0</v>
-      </c>
-      <c r="U2" s="6">
-        <v>0</v>
-      </c>
-      <c r="V2" s="6">
-        <v>0</v>
-      </c>
-      <c r="W2" s="6">
-        <v>0</v>
-      </c>
-      <c r="X2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="B2" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0</v>
+      </c>
+      <c r="R2" s="4">
+        <v>0</v>
+      </c>
+      <c r="S2" s="4">
+        <v>0</v>
+      </c>
+      <c r="T2" s="4">
+        <v>0</v>
+      </c>
+      <c r="U2" s="4">
+        <v>0</v>
+      </c>
+      <c r="V2" s="4">
+        <v>0</v>
+      </c>
+      <c r="W2" s="4">
+        <v>0</v>
+      </c>
+      <c r="X2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
-        <v>0</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="E3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="F3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="G3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="H3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="I3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="J3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="K3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="L3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="M3" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="N3" s="6">
-        <v>0.26</v>
-      </c>
-      <c r="O3" s="6">
-        <v>0.22</v>
-      </c>
-      <c r="P3" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="6">
-        <v>0</v>
-      </c>
-      <c r="R3" s="6">
-        <v>0</v>
-      </c>
-      <c r="S3" s="6">
-        <v>0</v>
-      </c>
-      <c r="T3" s="6">
-        <v>0</v>
-      </c>
-      <c r="U3" s="6">
-        <v>0</v>
-      </c>
-      <c r="V3" s="6">
-        <v>0</v>
-      </c>
-      <c r="W3" s="6">
-        <v>0</v>
-      </c>
-      <c r="X3" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="B3" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0</v>
+      </c>
+      <c r="R3" s="4">
+        <v>0</v>
+      </c>
+      <c r="S3" s="4">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4">
+        <v>0</v>
+      </c>
+      <c r="U3" s="4">
+        <v>0</v>
+      </c>
+      <c r="V3" s="4">
+        <v>0</v>
+      </c>
+      <c r="W3" s="4">
+        <v>0</v>
+      </c>
+      <c r="X3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
-        <v>0</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6">
-        <v>0</v>
-      </c>
-      <c r="K4" s="6">
-        <v>0</v>
-      </c>
-      <c r="L4" s="6">
-        <v>0</v>
-      </c>
-      <c r="M4" s="6">
-        <v>0</v>
-      </c>
-      <c r="N4" s="6">
-        <v>0</v>
-      </c>
-      <c r="O4" s="6">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6">
-        <v>0</v>
-      </c>
-      <c r="S4" s="6">
-        <v>0</v>
-      </c>
-      <c r="T4" s="6">
-        <v>0</v>
-      </c>
-      <c r="U4" s="6">
-        <v>0</v>
-      </c>
-      <c r="V4" s="6">
-        <v>0</v>
-      </c>
-      <c r="W4" s="6">
-        <v>0</v>
-      </c>
-      <c r="X4" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0</v>
+      </c>
+      <c r="R4" s="4">
+        <v>0</v>
+      </c>
+      <c r="S4" s="4">
+        <v>0</v>
+      </c>
+      <c r="T4" s="4">
+        <v>0</v>
+      </c>
+      <c r="U4" s="4">
+        <v>0</v>
+      </c>
+      <c r="V4" s="4">
+        <v>0</v>
+      </c>
+      <c r="W4" s="4">
+        <v>0</v>
+      </c>
+      <c r="X4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B7" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41BB044B-44BA-44BA-9460-CFA8BF0E5CDA}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24984820-0516-4D0B-94DC-C5A16038A85F}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1A7F3C9-EBF1-4FE2-8C6F-AC91F68C7627}"/>
 </file>